--- a/测试集(2)/excel模板测试.xlsx
+++ b/测试集(2)/excel模板测试.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A23\Intelligent-Document-Processing-System\测试集(2)\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF7CE7F-D350-42BC-A85A-22982B8BEF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2955" yWindow="3315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +24,42 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
+  <si>
+    <t>产品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>专业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产品名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -53,7 +87,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +364,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/测试集(2)/excel模板测试.xlsx
+++ b/测试集(2)/excel模板测试.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A23\Intelligent-Document-Processing-System\测试集(2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF7CE7F-D350-42BC-A85A-22982B8BEF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C21D6FA-1765-4A39-901C-BF18E227C985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2955" yWindow="3315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="840" yWindow="4485" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,29 +25,58 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="4">
-  <si>
-    <t>产品</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>职位属性</t>
+  </si>
+  <si>
+    <t>职位分布</t>
+  </si>
+  <si>
+    <t>职位简介</t>
+  </si>
+  <si>
+    <t>职位代码</t>
+  </si>
+  <si>
+    <t>机构层级</t>
+  </si>
+  <si>
+    <t>考试类别</t>
+  </si>
+  <si>
+    <t>招考人数</t>
   </si>
   <si>
     <t>专业</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>产品名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>姓名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学历</t>
+  </si>
+  <si>
+    <t>学位</t>
+  </si>
+  <si>
+    <t>政治面貌</t>
+  </si>
+  <si>
+    <t>基层工作最低年限</t>
+  </si>
+  <si>
+    <t>服务基层项目工作经历</t>
+  </si>
+  <si>
+    <t>是否在面试阶段组织专业能力测试</t>
+  </si>
+  <si>
+    <t>面试人员比例</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -57,6 +86,14 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -83,8 +120,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -365,24 +405,54 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
